--- a/docs/主控板引脚表(2).xlsx
+++ b/docs/主控板引脚表(2).xlsx
@@ -159,7 +159,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="43">
     <fill>
       <patternFill/>
     </fill>
@@ -397,6 +397,16 @@
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1E6F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -667,7 +677,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -736,6 +746,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="42" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1293,7 +1318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1308,6 +1333,8 @@
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1371,6 +1398,16 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="M1" s="24" t="inlineStr">
+        <is>
+          <t>syscfg 实例名(固件侧)</t>
+        </is>
+      </c>
+      <c r="N1" s="24" t="inlineStr">
+        <is>
+          <t>syscfg 引脚宏</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="n">
@@ -1429,6 +1466,16 @@
           <t>G3507/G3519 64脚位置一致</t>
         </is>
       </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>系统复位(BCR/ROM)</t>
+        </is>
+      </c>
+      <c r="N2" s="25" t="inlineStr">
+        <is>
+          <t>—(syscfg 不配置)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n">
@@ -1487,6 +1534,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M3" s="25" t="inlineStr">
+        <is>
+          <t>SWD 调试口</t>
+        </is>
+      </c>
+      <c r="N3" s="25" t="inlineStr">
+        <is>
+          <t>—(syscfg 不配置)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="n">
@@ -1545,6 +1602,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t>SWD 调试口</t>
+        </is>
+      </c>
+      <c r="N4" s="25" t="inlineStr">
+        <is>
+          <t>—(syscfg 不配置)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="n">
@@ -1603,6 +1670,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M5" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N5" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_STATUS_LED_PIN_22_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -1661,6 +1738,16 @@
           <t>仅BSL烧录，9600（ROM固定，不可调）。运行期固件不再配置UART0作他用——原备注『运行阶段UART0交给陀螺仪』已作废</t>
         </is>
       </c>
+      <c r="M6" s="25" t="inlineStr">
+        <is>
+          <t>UART_BSL_ENTRY (=UART0)</t>
+        </is>
+      </c>
+      <c r="N6" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_BSL_ENTRY_TX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -1719,6 +1806,16 @@
           <t>模块RX接PA10，模块TX接PA11。软件跳BSL的ENTRY字节为0x22（9600）</t>
         </is>
       </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t>UART_BSL_ENTRY (=UART0)</t>
+        </is>
+      </c>
+      <c r="N7" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_BSL_ENTRY_RX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -1777,6 +1874,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M8" s="25" t="inlineStr">
+        <is>
+          <t>UART_VISION (=UART1)</t>
+        </is>
+      </c>
+      <c r="N8" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_VISION_TX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -1835,6 +1942,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M9" s="25" t="inlineStr">
+        <is>
+          <t>UART_VISION (=UART1)</t>
+        </is>
+      </c>
+      <c r="N9" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_VISION_RX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26.4" customHeight="1">
       <c r="A10" s="10" t="n">
@@ -1893,6 +2010,16 @@
           <t>原理图不变，固件按芯片选择UART实例</t>
         </is>
       </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t>UART_STEPPER_BUS (=UART7)</t>
+        </is>
+      </c>
+      <c r="N10" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_STEPPER_BUS_TX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26.4" customHeight="1">
       <c r="A11" s="10" t="n">
@@ -1951,6 +2078,16 @@
           <t>同上</t>
         </is>
       </c>
+      <c r="M11" s="25" t="inlineStr">
+        <is>
+          <t>UART_STEPPER_BUS (=UART7)</t>
+        </is>
+      </c>
+      <c r="N11" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_STEPPER_BUS_RX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26.4" customHeight="1">
       <c r="A12" s="12" t="n">
@@ -2009,6 +2146,16 @@
           <t>固件已确认：陀螺仪=UART3/PA26(TX)。原脚号35实为PA28，疑为改向Sheet2方案时只改脚号未改引脚名</t>
         </is>
       </c>
+      <c r="M12" s="25" t="inlineStr">
+        <is>
+          <t>UART_IMU (=UART3)</t>
+        </is>
+      </c>
+      <c r="N12" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_IMU_TX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26.4" customHeight="1">
       <c r="A13" s="12" t="n">
@@ -2067,6 +2214,16 @@
           <t>固件已确认：陀螺仪=UART3/PA25(RX)。原脚号39实为PA31，同上。Sheet2第4行（迁PA28/PA31）已作废</t>
         </is>
       </c>
+      <c r="M13" s="25" t="inlineStr">
+        <is>
+          <t>UART_IMU (=UART3)</t>
+        </is>
+      </c>
+      <c r="N13" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_IMU_RX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26.4" customHeight="1">
       <c r="A14" s="10" t="n">
@@ -2125,6 +2282,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M14" s="25" t="inlineStr">
+        <is>
+          <t>I2C_AUX (=I2C1)</t>
+        </is>
+      </c>
+      <c r="N14" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_I2C_AUX_SDA_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26.4" customHeight="1">
       <c r="A15" s="10" t="n">
@@ -2183,6 +2350,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M15" s="25" t="inlineStr">
+        <is>
+          <t>I2C_AUX (=I2C1)</t>
+        </is>
+      </c>
+      <c r="N15" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_I2C_AUX_SCL_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -2241,6 +2418,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N16" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_GRP_KEY_K1_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -2299,6 +2486,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M17" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N17" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_GRP_KEY_K2_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -2357,6 +2554,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M18" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N18" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_GRP_KEY_K3_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -2415,6 +2622,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M19" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N19" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_GRP_KEY_K4_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="26.4" customHeight="1">
       <c r="A20" s="10" t="n">
@@ -2468,9 +2685,19 @@
           <t>变更</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>G3519硬件QEI；G3507软件QEI</t>
+      <c r="L20" s="26" t="inlineStr">
+        <is>
+          <t>G3519硬件QEI；G3507软件QEI 【⚠固件未跟进】表称 编码器，固件实为 GPIO 直连(无外设实例)（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M20" s="27" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N20" s="27" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN4_PIN</t>
         </is>
       </c>
     </row>
@@ -2526,9 +2753,19 @@
           <t>变更</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>G3519硬件QEI；G3507软件QEI</t>
+      <c r="L21" s="26" t="inlineStr">
+        <is>
+          <t>G3519硬件QEI；G3507软件QEI 【⚠固件未跟进】表称 编码器，固件实为 GPIO 直连(无外设实例)（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M21" s="27" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N21" s="27" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN5_PIN</t>
         </is>
       </c>
     </row>
@@ -2584,9 +2821,19 @@
           <t>变更</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>G3507/G3519均为TIMG8硬件QEI</t>
+      <c r="L22" s="26" t="inlineStr">
+        <is>
+          <t>G3507/G3519均为TIMG8硬件QEI 【⚠固件未跟进】表称 编码器，固件实为 GPIO 直连(无外设实例)（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M22" s="27" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N22" s="27" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN10_PIN</t>
         </is>
       </c>
     </row>
@@ -2642,9 +2889,19 @@
           <t>变更</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>G3507/G3519均为TIMG8硬件QEI</t>
+      <c r="L23" s="26" t="inlineStr">
+        <is>
+          <t>G3507/G3519均为TIMG8硬件QEI 【⚠固件未跟进】表称 编码器，固件实为 GPIO 直连(无外设实例)（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M23" s="27" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N23" s="27" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN11_PIN</t>
         </is>
       </c>
     </row>
@@ -2705,6 +2962,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M24" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N24" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_DRIVE_DIR_AIN1_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
@@ -2763,6 +3030,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M25" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N25" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_DRIVE_DIR_AIN2_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -2821,6 +3098,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M26" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N26" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_DRIVE_DIR_BIN1_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
@@ -2879,6 +3166,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M27" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N27" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_DRIVE_DIR_BIN2_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -2937,6 +3234,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M28" s="25" t="inlineStr">
+        <is>
+          <t>PWM_DRIVE_LEFT (=TIMA0)</t>
+        </is>
+      </c>
+      <c r="N28" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_PWM_DRIVE_LEFT_C1_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -2995,6 +3302,16 @@
           <t>两芯片一致</t>
         </is>
       </c>
+      <c r="M29" s="25" t="inlineStr">
+        <is>
+          <t>PWM_DRIVE_RIGHT (=TIMA1)</t>
+        </is>
+      </c>
+      <c r="N29" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_PWM_DRIVE_RIGHT_C0_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
@@ -3049,6 +3366,16 @@
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr"/>
+      <c r="M30" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N30" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN1_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
@@ -3103,6 +3430,16 @@
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N31" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN2_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
@@ -3157,6 +3494,16 @@
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr"/>
+      <c r="M32" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N32" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN3_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
@@ -3210,9 +3557,19 @@
           <t>变更</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>原PB7让给TIMG9，迁移到PA7</t>
+      <c r="L33" s="26" t="inlineStr">
+        <is>
+          <t>原PB7让给TIMG9，迁移到PA7 【⚠固件未跟进】表称 12路灰度，固件实为 QEI_LEFT (=TIMG8)（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M33" s="27" t="inlineStr">
+        <is>
+          <t>QEI_LEFT (=TIMG8)</t>
+        </is>
+      </c>
+      <c r="N33" s="27" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_LEFT_PHA_PIN</t>
         </is>
       </c>
     </row>
@@ -3268,9 +3625,19 @@
           <t>变更</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>原PB9让给TIMG9，迁移到PB20</t>
+      <c r="L34" s="26" t="inlineStr">
+        <is>
+          <t>原PB9让给TIMG9，迁移到PB20 【⚠固件未跟进】表称 12路灰度，固件实为 —(board.syscfg 未配置)（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M34" s="27" t="inlineStr">
+        <is>
+          <t>—(board.syscfg 未配置)</t>
+        </is>
+      </c>
+      <c r="N34" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3327,6 +3694,16 @@
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr"/>
+      <c r="M35" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N35" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN6_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -3381,6 +3758,16 @@
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr"/>
+      <c r="M36" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N36" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN7_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -3435,6 +3822,16 @@
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr"/>
+      <c r="M37" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N37" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN8_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
@@ -3489,6 +3886,16 @@
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr"/>
+      <c r="M38" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N38" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN9_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
@@ -3542,9 +3949,19 @@
           <t>变更</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>原PB10让给TIMG8，迁移到PB14</t>
+      <c r="L39" s="26" t="inlineStr">
+        <is>
+          <t>原PB10让给TIMG8，迁移到PB14 【⚠固件未跟进】表称 12路灰度，固件实为 —(board.syscfg 未配置)（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M39" s="27" t="inlineStr">
+        <is>
+          <t>—(board.syscfg 未配置)</t>
+        </is>
+      </c>
+      <c r="N39" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3600,9 +4017,19 @@
           <t>变更</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>原PB11让给TIMG8，迁移到PB0</t>
+      <c r="L40" s="26" t="inlineStr">
+        <is>
+          <t>原PB11让给TIMG8，迁移到PB0 【⚠固件未跟进】表称 12路灰度，固件实为 —(board.syscfg 未配置)（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M40" s="27" t="inlineStr">
+        <is>
+          <t>—(board.syscfg 未配置)</t>
+        </is>
+      </c>
+      <c r="N40" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3659,6 +4086,16 @@
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr"/>
+      <c r="M41" s="25" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N41" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN12_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="n">
@@ -3717,6 +4154,16 @@
           <t>【作废】PA26 已归陀螺仪。调试串口迁至新增的 UART5/PA1，见第46行</t>
         </is>
       </c>
+      <c r="M42" s="25" t="inlineStr">
+        <is>
+          <t>UART_IMU (=UART3)</t>
+        </is>
+      </c>
+      <c r="N42" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_IMU_TX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="n">
@@ -3775,6 +4222,16 @@
           <t>【作废】PA25 已归陀螺仪。调试串口迁至新增的 UART5/PA0，见第47行</t>
         </is>
       </c>
+      <c r="M43" s="25" t="inlineStr">
+        <is>
+          <t>UART_IMU (=UART3)</t>
+        </is>
+      </c>
+      <c r="N43" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_IMU_RX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
@@ -3828,9 +4285,19 @@
           <t>释放</t>
         </is>
       </c>
-      <c r="L44" s="16" t="inlineStr">
-        <is>
-          <t>不再用于编码器，避免核心板晶振功能冲突</t>
+      <c r="L44" s="28" t="inlineStr">
+        <is>
+          <t>不再用于编码器，避免核心板晶振功能冲突 【⚠固件未跟进】表称已释放，但固件仍占用（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M44" s="27" t="inlineStr">
+        <is>
+          <t>QEI_LEFT (=TIMG8)</t>
+        </is>
+      </c>
+      <c r="N44" s="27" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_LEFT_PHB_PIN</t>
         </is>
       </c>
     </row>
@@ -3886,9 +4353,19 @@
           <t>释放</t>
         </is>
       </c>
-      <c r="L45" s="16" t="inlineStr">
-        <is>
-          <t>不再用于编码器</t>
+      <c r="L45" s="28" t="inlineStr">
+        <is>
+          <t>不再用于编码器 【⚠固件未跟进】表称已释放，但固件仍占用（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M45" s="27" t="inlineStr">
+        <is>
+          <t>QEI_RIGHT (=TIMG9)</t>
+        </is>
+      </c>
+      <c r="N45" s="27" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_RIGHT_PHA_PIN</t>
         </is>
       </c>
     </row>
@@ -3944,9 +4421,19 @@
           <t>释放</t>
         </is>
       </c>
-      <c r="L46" s="16" t="inlineStr">
-        <is>
-          <t>不再用于编码器</t>
+      <c r="L46" s="28" t="inlineStr">
+        <is>
+          <t>不再用于编码器 【⚠固件未跟进】表称已释放，但固件仍占用（Q4 编码器⇄灰度对调尚未施工）</t>
+        </is>
+      </c>
+      <c r="M46" s="27" t="inlineStr">
+        <is>
+          <t>QEI_RIGHT (=TIMG9)</t>
+        </is>
+      </c>
+      <c r="N46" s="27" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_RIGHT_PHB_PIN</t>
         </is>
       </c>
     </row>
@@ -4007,6 +4494,16 @@
           <t>★硬件组需新引出：VOFA上下位机实时调参串口。UART5在LQFP-64/100下均存在，不受封装争议影响</t>
         </is>
       </c>
+      <c r="M47" s="25" t="inlineStr">
+        <is>
+          <t>UART_HOST_LINK (=UART5)</t>
+        </is>
+      </c>
+      <c r="N47" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_HOST_LINK_TX_PIN</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="20" t="n">
@@ -4063,6 +4560,16 @@
       <c r="L48" s="21" t="inlineStr">
         <is>
           <t>★硬件组需新引出。固件已就绪（board.syscfg 提交 ae215b1），引出前实物上VOFA不通</t>
+        </is>
+      </c>
+      <c r="M48" s="25" t="inlineStr">
+        <is>
+          <t>UART_HOST_LINK (=UART5)</t>
+        </is>
+      </c>
+      <c r="N48" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_HOST_LINK_RX_PIN</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4409,44 +4916,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>脚号订正</t>
+          <t>新增列</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>第5行 PA10</t>
+          <t>Sheet1 M/N 列</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>58 -&gt; 56</t>
+          <t>syscfg 实例名 + 引脚宏</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 58 实为其他引脚的脚号</t>
+          <t>固件侧标识，供硬件组与固件对齐命名。全部取自 SysConfig 生成的 Debug/ti_msp_dl_config.h（非人工拼接），以 IOMUX_PINCM 关联引脚，每个宏均已回验在头文件中真实定义。共 41 个引脚有宏。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>脚号订正</t>
+          <t>★冲突标注</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>第6行 PA11</t>
+          <t>Sheet1 橙色行（共 11 行）</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>59 -&gt; 57</t>
+          <t>表里的功能 ≠ 固件 syscfg 实际归属</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 59 实为其他引脚的脚号</t>
+          <t>M/N 两列反映的是【固件当前实际状态】，不是表的诉求。橙色行表示两者不一致，根因是 Q4（编码器⇄灰度引脚对调）尚未施工：固件里 PB7/PB9/PB10/PB11 仍是灰度 IN4/IN5/IN10/IN11，PA7/PA6/PA3/PA2 仍是编码器 QEI_LEFT/QEI_RIGHT，而 PB20/PB14/PB0 尚未配置。待 Q4 获硬件组确认并施工后，这些行会自动一致。此标注不是错误，是进度差异。</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4965,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>第7行 PA8</t>
+          <t>第5行 PA10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>56 -&gt; 54</t>
+          <t>58 -&gt; 56</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 56 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 58 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
@@ -4480,17 +4987,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>第8行 PA9</t>
+          <t>第6行 PA11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57 -&gt; 55</t>
+          <t>59 -&gt; 57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 57 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 59 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
@@ -4502,17 +5009,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>第11行 PA26</t>
+          <t>第7行 PA8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>35 -&gt; 30</t>
+          <t>56 -&gt; 54</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 35 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 56 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
@@ -4524,17 +5031,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>第12行 PA25</t>
+          <t>第8行 PA9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>39 -&gt; 26</t>
+          <t>57 -&gt; 55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 39 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 57 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
@@ -4546,105 +5053,105 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>第19行 PB7</t>
+          <t>第11行 PA26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>55 -&gt; 59</t>
+          <t>35 -&gt; 30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 55 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 35 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>用途变更</t>
+          <t>脚号订正</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>第5/6行 PA10/PA11</t>
+          <t>第12行 PA25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>运行期UART0交陀螺仪 -&gt; 仅BSL烧录</t>
+          <t>39 -&gt; 26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>用户2026-07-16裁定；固件已配 UART_BSL_ENTRY=UART0/9600/无DMA</t>
+          <t>TI 器件数据为准；原值 39 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>裁定确认</t>
+          <t>脚号订正</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>第11/12行 陀螺仪</t>
+          <t>第19行 PB7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UART3 PA26/PA25（维持）</t>
+          <t>55 -&gt; 59</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>用户2026-07-16裁定；board.syscfg 现状即如此，固件零改动</t>
+          <t>TI 器件数据为准；原值 55 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>作废</t>
+          <t>用途变更</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>第41/42行 调试串口</t>
+          <t>第5/6行 PA10/PA11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PA26/PA25 -&gt; 作废</t>
+          <t>运行期UART0交陀螺仪 -&gt; 仅BSL烧录</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PA25/PA26 归陀螺仪独占；『与陀螺仪分离』无法在同一对引脚上成立</t>
+          <t>用户2026-07-16裁定；固件已配 UART_BSL_ENTRY=UART0/9600/无DMA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>裁定确认</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>第46/47行 VOFA调试串口</t>
+          <t>第11/12行 陀螺仪</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UART5 PA1(TX,脚34)/PA0(RX,脚33) @230400</t>
+          <t>UART3 PA26/PA25（维持）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>★需硬件组新引出；用户2026-07-16裁定</t>
+          <t>用户2026-07-16裁定；board.syscfg 现状即如此，固件零改动</t>
         </is>
       </c>
     </row>
@@ -4656,62 +5163,83 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sheet2第4行</t>
+          <t>第41/42行 调试串口</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>陀螺仪迁PA28/PA31 -&gt; 作废</t>
+          <t>PA26/PA25 -&gt; 作废</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>用户裁定陀螺仪维持PA25/PA26</t>
+          <t>PA25/PA26 归陀螺仪独占；『与陀螺仪分离』无法在同一对引脚上成立</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>修正</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sheet2第5行</t>
+          <t>第46/47行 VOFA调试串口</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>运行期UART0交陀螺仪 -&gt; 运行期UART0不使用</t>
+          <t>UART5 PA1(TX,脚34)/PA0(RX,脚33) @230400</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VOFA 迁 UART5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>★需硬件组新引出；用户2026-07-16裁定</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>作废</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sheet2第4行</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>陀螺仪迁PA28/PA31 -&gt; 作废</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>用户裁定陀螺仪维持PA25/PA26</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【图例】</t>
+          <t>修正</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>黄=脚号订正</t>
+          <t>Sheet2第5行</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>绿=新增需求(需硬件组动作)</t>
+          <t>运行期UART0交陀螺仪 -&gt; 运行期UART0不使用</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>红=作废</t>
+          <t>VOFA 迁 UART5</t>
         </is>
       </c>
     </row>
@@ -4719,71 +5247,94 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【仍待硬件组答复】</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Q1 封装</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sheet2第6行</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>表称统一LQFP-64(PM)；工程board.syscfg配置为LQFP-100(PZ)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>G3519 两种封装都存在，故这是真问题。已核实：两颗芯片LQFP-64下64个脚号对应引脚名完全一致，故Sheet2第6行的兼容性前提成立。但打样实物到底是哪个封装需确认</t>
-        </is>
-      </c>
-    </row>
+          <t>【图例】</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>黄=脚号订正</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>绿=新增需求(需硬件组动作)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>橙=表与固件当前不一致(Q4 未施工)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q4 编码器⇄灰度对调</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Sheet1第19-22/32/33/38/39行</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>是否按表执行？PA6晶振冲突是否实测确认？</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>★高风险：本次对调同时翻转了timer↔轮归属（现LEFT=TIMG8/RIGHT=TIMG9，表要求左轮=TIMG9/右轮=TIMG8）。若只改引脚不改映射，左右轮数据会静默对调——不报错不崩溃，易误判为PID问题</t>
+          <t>【仍待硬件组答复】</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Q1 封装</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sheet2第6行</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>表称统一LQFP-64(PM)；工程board.syscfg配置为LQFP-100(PZ)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>G3519 两种封装都存在，故这是真问题。已核实：两颗芯片LQFP-64下64个脚号对应引脚名完全一致，故Sheet2第6行的兼容性前提成立。但打样实物到底是哪个封装需确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q4 编码器⇄灰度对调</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sheet1第19-22/32/33/38/39行</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>是否按表执行？PA6晶振冲突是否实测确认？</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>★高风险：本次对调同时翻转了timer↔轮归属（现LEFT=TIMG8/RIGHT=TIMG9，表要求左轮=TIMG9/右轮=TIMG8）。若只改引脚不改映射，左右轮数据会静默对调——不报错不崩溃，易误判为PID问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>脚号错误</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Sheet1 共7行</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>PA8/PA9/PA10/PA11 整体偏移+2；PB7 偏差-4；PA26/PA25 填成了PA28/PA31的脚号</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>★请核对PCB实物：若布线是照脚号走的，则无线模块实际接到PB6/PB7而非PA10/PA11。若布线照原理图符号走则仅为文档错误</t>
         </is>

--- a/docs/主控板引脚表(2).xlsx
+++ b/docs/主控板引脚表(2).xlsx
@@ -677,7 +677,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -760,6 +760,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="42" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1318,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2634,274 +2652,274 @@
       </c>
     </row>
     <row r="20" ht="26.4" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>编码器-左轮</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>A相</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>B07</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>PB7</t>
         </is>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="21" t="n">
         <v>59</v>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>G3519 TIMG9.C0 / G3507 GPIO IRQ</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>3.3V方波</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>U33.3</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="L20" s="26" t="inlineStr">
-        <is>
-          <t>G3519硬件QEI；G3507软件QEI 【⚠固件未跟进】表称 编码器，固件实为 GPIO 直连(无外设实例)（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M20" s="27" t="inlineStr">
-        <is>
-          <t>GPIO 直连(无外设实例)</t>
-        </is>
-      </c>
-      <c r="N20" s="27" t="inlineStr">
-        <is>
-          <t>GPIO_LINE_SENSOR_PIN_IN4_PIN</t>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>已施工</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>G3519硬件QEI；G3507软件QEI</t>
+        </is>
+      </c>
+      <c r="M20" s="29" t="inlineStr">
+        <is>
+          <t>QEI_LEFT (=TIMG9)</t>
+        </is>
+      </c>
+      <c r="N20" s="29" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_LEFT_PHA_PIN</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26.4" customHeight="1">
-      <c r="A21" s="13" t="n">
+      <c r="A21" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>编码器-左轮</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B相</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>B09</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>PB9</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="21" t="n">
         <v>61</v>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>G3519 TIMG9.C1 / G3507 GPIO IRQ</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>3.3V方波</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="J21" s="21" t="inlineStr">
         <is>
           <t>U33.4</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="L21" s="26" t="inlineStr">
-        <is>
-          <t>G3519硬件QEI；G3507软件QEI 【⚠固件未跟进】表称 编码器，固件实为 GPIO 直连(无外设实例)（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M21" s="27" t="inlineStr">
-        <is>
-          <t>GPIO 直连(无外设实例)</t>
-        </is>
-      </c>
-      <c r="N21" s="27" t="inlineStr">
-        <is>
-          <t>GPIO_LINE_SENSOR_PIN_IN5_PIN</t>
+      <c r="K21" s="30" t="inlineStr">
+        <is>
+          <t>已施工</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>G3519硬件QEI；G3507软件QEI</t>
+        </is>
+      </c>
+      <c r="M21" s="29" t="inlineStr">
+        <is>
+          <t>QEI_LEFT (=TIMG9)</t>
+        </is>
+      </c>
+      <c r="N21" s="29" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_LEFT_PHB_PIN</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="n">
+      <c r="A22" s="20" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>编码器-右轮</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>A相</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>PB10</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="21" t="n">
         <v>62</v>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>TIMG8.C0(QEI PHA)</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>3.3V方波</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>U34.3</t>
         </is>
       </c>
-      <c r="K22" s="14" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="L22" s="26" t="inlineStr">
-        <is>
-          <t>G3507/G3519均为TIMG8硬件QEI 【⚠固件未跟进】表称 编码器，固件实为 GPIO 直连(无外设实例)（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M22" s="27" t="inlineStr">
-        <is>
-          <t>GPIO 直连(无外设实例)</t>
-        </is>
-      </c>
-      <c r="N22" s="27" t="inlineStr">
-        <is>
-          <t>GPIO_LINE_SENSOR_PIN_IN10_PIN</t>
+      <c r="K22" s="30" t="inlineStr">
+        <is>
+          <t>已施工</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>G3507/G3519均为TIMG8硬件QEI</t>
+        </is>
+      </c>
+      <c r="M22" s="29" t="inlineStr">
+        <is>
+          <t>QEI_RIGHT (=TIMG8)</t>
+        </is>
+      </c>
+      <c r="N22" s="29" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_RIGHT_PHA_PIN</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="n">
+      <c r="A23" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>编码器-右轮</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B相</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>B11</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>PB11</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="21" t="n">
         <v>63</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>TIMG8.C1(QEI PHB)</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>3.3V方波</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>U34.4</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="L23" s="26" t="inlineStr">
-        <is>
-          <t>G3507/G3519均为TIMG8硬件QEI 【⚠固件未跟进】表称 编码器，固件实为 GPIO 直连(无外设实例)（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M23" s="27" t="inlineStr">
-        <is>
-          <t>GPIO 直连(无外设实例)</t>
-        </is>
-      </c>
-      <c r="N23" s="27" t="inlineStr">
-        <is>
-          <t>GPIO_LINE_SENSOR_PIN_IN11_PIN</t>
+      <c r="K23" s="30" t="inlineStr">
+        <is>
+          <t>已施工</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>G3507/G3519均为TIMG8硬件QEI</t>
+        </is>
+      </c>
+      <c r="M23" s="29" t="inlineStr">
+        <is>
+          <t>QEI_RIGHT (=TIMG8)</t>
+        </is>
+      </c>
+      <c r="N23" s="29" t="inlineStr">
+        <is>
+          <t>GPIO_QEI_RIGHT_PHB_PIN</t>
         </is>
       </c>
     </row>
@@ -3506,138 +3524,140 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>12路灰度</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>IN4</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>A07</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>PA7</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>B08</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>PB8</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>GPIO输入</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>3.3V数字</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
+      <c r="J33" s="21" t="inlineStr">
         <is>
           <t>12路灰度.4</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="L33" s="26" t="inlineStr">
-        <is>
-          <t>原PB7让给TIMG9，迁移到PA7 【⚠固件未跟进】表称 12路灰度，固件实为 QEI_LEFT (=TIMG8)（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M33" s="27" t="inlineStr">
-        <is>
-          <t>QEI_LEFT (=TIMG8)</t>
-        </is>
-      </c>
-      <c r="N33" s="27" t="inlineStr">
-        <is>
-          <t>GPIO_QEI_LEFT_PHA_PIN</t>
+      <c r="K33" s="21" t="inlineStr">
+        <is>
+          <t>已施工</t>
+        </is>
+      </c>
+      <c r="L33" s="31" t="inlineStr">
+        <is>
+          <t>原PB7让给编码器QEI。固件裁定迁 PB8（不是早前设想的 PA7）：12路灰度必须全部留在 PORTB —— SysConfig 仅在同组同端口时生成组级单端口宏 GPIO_LINE_SENSOR_PORT，固件靠它一次原子读取全部12路；跨到 PORTA 会使该宏消失且12路无法同刻采样。PB8 是 PB7 的物理邻脚（LQFP-64: 59→60），布线改动最小。</t>
+        </is>
+      </c>
+      <c r="M33" s="29" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N33" s="29" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN4_PIN</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>12路灰度</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>IN5</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>B20</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>PB20</t>
         </is>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>GPIO输入</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>3.3V数字</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J34" s="21" t="inlineStr">
         <is>
           <t>12路灰度.5</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="L34" s="26" t="inlineStr">
-        <is>
-          <t>原PB9让给TIMG9，迁移到PB20 【⚠固件未跟进】表称 12路灰度，固件实为 —(board.syscfg 未配置)（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M34" s="27" t="inlineStr">
-        <is>
-          <t>—(board.syscfg 未配置)</t>
-        </is>
-      </c>
-      <c r="N34" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>已施工</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>原PB9让给TIMG9，迁移到PB20</t>
+        </is>
+      </c>
+      <c r="M34" s="29" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N34" s="29" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN5_PIN</t>
         </is>
       </c>
     </row>
@@ -3898,138 +3918,138 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n">
+      <c r="A39" s="20" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>12路灰度</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>IN10</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>B14</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>PB14</t>
         </is>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>GPIO输入</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I39" s="21" t="inlineStr">
         <is>
           <t>3.3V数字</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="J39" s="21" t="inlineStr">
         <is>
           <t>12路灰度.10</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="L39" s="26" t="inlineStr">
-        <is>
-          <t>原PB10让给TIMG8，迁移到PB14 【⚠固件未跟进】表称 12路灰度，固件实为 —(board.syscfg 未配置)（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M39" s="27" t="inlineStr">
-        <is>
-          <t>—(board.syscfg 未配置)</t>
-        </is>
-      </c>
-      <c r="N39" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K39" s="21" t="inlineStr">
+        <is>
+          <t>已施工</t>
+        </is>
+      </c>
+      <c r="L39" s="21" t="inlineStr">
+        <is>
+          <t>原PB10让给TIMG8，迁移到PB14</t>
+        </is>
+      </c>
+      <c r="M39" s="29" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N39" s="29" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN10_PIN</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
+      <c r="A40" s="20" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>12路灰度</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>IN11</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>B00</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="21" t="inlineStr">
         <is>
           <t>PB0</t>
         </is>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="21" t="n">
         <v>47</v>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="21" t="inlineStr">
         <is>
           <t>GPIO输入</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="H40" s="21" t="inlineStr">
         <is>
           <t>输入</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="21" t="inlineStr">
         <is>
           <t>3.3V数字</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="J40" s="21" t="inlineStr">
         <is>
           <t>12路灰度.11</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="L40" s="26" t="inlineStr">
-        <is>
-          <t>原PB11让给TIMG8，迁移到PB0 【⚠固件未跟进】表称 12路灰度，固件实为 —(board.syscfg 未配置)（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M40" s="27" t="inlineStr">
-        <is>
-          <t>—(board.syscfg 未配置)</t>
-        </is>
-      </c>
-      <c r="N40" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K40" s="21" t="inlineStr">
+        <is>
+          <t>已施工</t>
+        </is>
+      </c>
+      <c r="L40" s="21" t="inlineStr">
+        <is>
+          <t>原PB11让给TIMG8，迁移到PB0</t>
+        </is>
+      </c>
+      <c r="M40" s="29" t="inlineStr">
+        <is>
+          <t>GPIO 直连(无外设实例)</t>
+        </is>
+      </c>
+      <c r="N40" s="29" t="inlineStr">
+        <is>
+          <t>GPIO_LINE_SENSOR_PIN_IN11_PIN</t>
         </is>
       </c>
     </row>
@@ -4098,138 +4118,138 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>调试串口(3V3)</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>UART3发送</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>A26</t>
-        </is>
-      </c>
-      <c r="E42" s="19" t="inlineStr">
-        <is>
-          <t>PA26</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G42" s="19" t="inlineStr">
-        <is>
-          <t>UART3.TX</t>
-        </is>
-      </c>
-      <c r="H42" s="19" t="inlineStr">
-        <is>
-          <t>输出</t>
-        </is>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>3.3V TTL</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
-        <is>
-          <t>调试串口.4</t>
-        </is>
-      </c>
-      <c r="K42" s="19" t="inlineStr">
-        <is>
-          <t>作废</t>
-        </is>
-      </c>
-      <c r="L42" s="19" t="inlineStr">
-        <is>
-          <t>【作废】PA26 已归陀螺仪。调试串口迁至新增的 UART5/PA1，见第46行</t>
-        </is>
-      </c>
-      <c r="M42" s="25" t="inlineStr">
-        <is>
-          <t>UART_IMU (=UART3)</t>
-        </is>
-      </c>
-      <c r="N42" s="25" t="inlineStr">
-        <is>
-          <t>GPIO_UART_IMU_TX_PIN</t>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>已释放/扩展</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>原QEI候选</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>PA6</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>46</v>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>GPIO/其他复用</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>扩展备用</t>
+        </is>
+      </c>
+      <c r="K42" s="16" t="inlineStr">
+        <is>
+          <t>已释放</t>
+        </is>
+      </c>
+      <c r="L42" s="32" t="inlineStr">
+        <is>
+          <t>PA6 = SYSCTL.HFXOUT（高频晶振输出），核心板实焊晶振，不可作数字输入 —— 编码器因此迁出。已释放，可作扩展。</t>
+        </is>
+      </c>
+      <c r="M42" s="33" t="inlineStr">
+        <is>
+          <t>—(board.syscfg 未配置/已释放)</t>
+        </is>
+      </c>
+      <c r="N42" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="19" t="inlineStr">
-        <is>
-          <t>调试串口(3V3)</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="inlineStr">
-        <is>
-          <t>UART3接收</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>A25</t>
-        </is>
-      </c>
-      <c r="E43" s="19" t="inlineStr">
-        <is>
-          <t>PA25</t>
-        </is>
-      </c>
-      <c r="F43" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="G43" s="19" t="inlineStr">
-        <is>
-          <t>UART3.RX</t>
-        </is>
-      </c>
-      <c r="H43" s="19" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="I43" s="19" t="inlineStr">
-        <is>
-          <t>3.3V TTL</t>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>调试串口.3</t>
-        </is>
-      </c>
-      <c r="K43" s="19" t="inlineStr">
-        <is>
-          <t>作废</t>
-        </is>
-      </c>
-      <c r="L43" s="19" t="inlineStr">
-        <is>
-          <t>【作废】PA25 已归陀螺仪。调试串口迁至新增的 UART5/PA0，见第47行</t>
-        </is>
-      </c>
-      <c r="M43" s="25" t="inlineStr">
-        <is>
-          <t>UART_IMU (=UART3)</t>
-        </is>
-      </c>
-      <c r="N43" s="25" t="inlineStr">
-        <is>
-          <t>GPIO_UART_IMU_RX_PIN</t>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>已释放/扩展</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>原QEI候选</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>PA3</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
+          <t>GPIO/其他复用</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>扩展备用</t>
+        </is>
+      </c>
+      <c r="K43" s="16" t="inlineStr">
+        <is>
+          <t>已释放</t>
+        </is>
+      </c>
+      <c r="L43" s="32" t="inlineStr">
+        <is>
+          <t>PA3 = SYSCTL.LFXIN（低频晶振输入），同上。已释放，可作扩展。</t>
+        </is>
+      </c>
+      <c r="M43" s="33" t="inlineStr">
+        <is>
+          <t>—(board.syscfg 未配置/已释放)</t>
+        </is>
+      </c>
+      <c r="N43" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4269,16 @@
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>A06</t>
+          <t>A02</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>PA6</t>
+          <t>PA2</t>
         </is>
       </c>
       <c r="F44" s="16" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
@@ -4282,22 +4302,22 @@
       </c>
       <c r="K44" s="16" t="inlineStr">
         <is>
-          <t>释放</t>
-        </is>
-      </c>
-      <c r="L44" s="28" t="inlineStr">
-        <is>
-          <t>不再用于编码器，避免核心板晶振功能冲突 【⚠固件未跟进】表称已释放，但固件仍占用（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M44" s="27" t="inlineStr">
-        <is>
-          <t>QEI_LEFT (=TIMG8)</t>
-        </is>
-      </c>
-      <c r="N44" s="27" t="inlineStr">
-        <is>
-          <t>GPIO_QEI_LEFT_PHB_PIN</t>
+          <t>已释放</t>
+        </is>
+      </c>
+      <c r="L44" s="32" t="inlineStr">
+        <is>
+          <t>PA2 = SYSCTL.ROSC（振荡器外接电阻），同上。已释放，可作扩展。</t>
+        </is>
+      </c>
+      <c r="M44" s="33" t="inlineStr">
+        <is>
+          <t>—(board.syscfg 未配置/已释放)</t>
+        </is>
+      </c>
+      <c r="N44" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -4317,16 +4337,18 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>A03</t>
+          <t>A07</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>PA3</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>43</v>
+          <t>PA7</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
@@ -4350,90 +4372,90 @@
       </c>
       <c r="K45" s="16" t="inlineStr">
         <is>
-          <t>释放</t>
-        </is>
-      </c>
-      <c r="L45" s="28" t="inlineStr">
-        <is>
-          <t>不再用于编码器 【⚠固件未跟进】表称已释放，但固件仍占用（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M45" s="27" t="inlineStr">
-        <is>
-          <t>QEI_RIGHT (=TIMG9)</t>
-        </is>
-      </c>
-      <c r="N45" s="27" t="inlineStr">
-        <is>
-          <t>GPIO_QEI_RIGHT_PHA_PIN</t>
+          <t>已释放</t>
+        </is>
+      </c>
+      <c r="L45" s="32" t="inlineStr">
+        <is>
+          <t>原 QEI_LEFT.PHA。随编码器整组迁出 PORTB 而释放（PA7 本身不是晶振脚，带 SYSCTL.CLK_OUT/FCC_IN，可用于时钟输出调试）。</t>
+        </is>
+      </c>
+      <c r="M45" s="33" t="inlineStr">
+        <is>
+          <t>—(board.syscfg 未配置/已释放)</t>
+        </is>
+      </c>
+      <c r="N45" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="n">
+      <c r="A46" s="20" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>已释放/扩展</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>原QEI候选</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="E46" s="16" t="inlineStr">
-        <is>
-          <t>PA2</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="G46" s="16" t="inlineStr">
-        <is>
-          <t>GPIO/其他复用</t>
-        </is>
-      </c>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>双向</t>
-        </is>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>3.3V</t>
-        </is>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>扩展备用</t>
-        </is>
-      </c>
-      <c r="K46" s="16" t="inlineStr">
-        <is>
-          <t>释放</t>
-        </is>
-      </c>
-      <c r="L46" s="28" t="inlineStr">
-        <is>
-          <t>不再用于编码器 【⚠固件未跟进】表称已释放，但固件仍占用（Q4 编码器⇄灰度对调尚未施工）</t>
-        </is>
-      </c>
-      <c r="M46" s="27" t="inlineStr">
-        <is>
-          <t>QEI_RIGHT (=TIMG9)</t>
-        </is>
-      </c>
-      <c r="N46" s="27" t="inlineStr">
-        <is>
-          <t>GPIO_QEI_RIGHT_PHB_PIN</t>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>调试串口/VOFA(UART5)</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>UART5发送→上位机RX</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t>PA1</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>UART5.TX</t>
+        </is>
+      </c>
+      <c r="H46" s="21" t="inlineStr">
+        <is>
+          <t>输出</t>
+        </is>
+      </c>
+      <c r="I46" s="21" t="inlineStr">
+        <is>
+          <t>3.3V TTL 230400</t>
+        </is>
+      </c>
+      <c r="J46" s="21" t="inlineStr">
+        <is>
+          <t>需新增引出</t>
+        </is>
+      </c>
+      <c r="K46" s="21" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="L46" s="21" t="inlineStr">
+        <is>
+          <t>★硬件组需新引出：VOFA上下位机实时调参串口。UART5在LQFP-64/100下均存在，不受封装争议影响</t>
+        </is>
+      </c>
+      <c r="M46" s="25" t="inlineStr">
+        <is>
+          <t>UART_HOST_LINK (=UART5)</t>
+        </is>
+      </c>
+      <c r="N46" s="25" t="inlineStr">
+        <is>
+          <t>GPIO_UART_HOST_LINK_TX_PIN</t>
         </is>
       </c>
     </row>
@@ -4448,30 +4470,30 @@
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>UART5发送→上位机RX</t>
+          <t>UART5接收←上位机TX</t>
         </is>
       </c>
       <c r="D47" s="21" t="inlineStr">
         <is>
-          <t>A01</t>
+          <t>A00</t>
         </is>
       </c>
       <c r="E47" s="21" t="inlineStr">
         <is>
-          <t>PA1</t>
+          <t>PA0</t>
         </is>
       </c>
       <c r="F47" s="21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
-          <t>UART5.TX</t>
+          <t>UART5.RX</t>
         </is>
       </c>
       <c r="H47" s="21" t="inlineStr">
         <is>
-          <t>输出</t>
+          <t>输入</t>
         </is>
       </c>
       <c r="I47" s="21" t="inlineStr">
@@ -4491,7 +4513,7 @@
       </c>
       <c r="L47" s="21" t="inlineStr">
         <is>
-          <t>★硬件组需新引出：VOFA上下位机实时调参串口。UART5在LQFP-64/100下均存在，不受封装争议影响</t>
+          <t>★硬件组需新引出。固件已就绪（board.syscfg 提交 ae215b1），引出前实物上VOFA不通</t>
         </is>
       </c>
       <c r="M47" s="25" t="inlineStr">
@@ -4500,74 +4522,6 @@
         </is>
       </c>
       <c r="N47" s="25" t="inlineStr">
-        <is>
-          <t>GPIO_UART_HOST_LINK_TX_PIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="21" t="inlineStr">
-        <is>
-          <t>调试串口/VOFA(UART5)</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>UART5接收←上位机TX</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>A00</t>
-        </is>
-      </c>
-      <c r="E48" s="21" t="inlineStr">
-        <is>
-          <t>PA0</t>
-        </is>
-      </c>
-      <c r="F48" s="21" t="n">
-        <v>33</v>
-      </c>
-      <c r="G48" s="21" t="inlineStr">
-        <is>
-          <t>UART5.RX</t>
-        </is>
-      </c>
-      <c r="H48" s="21" t="inlineStr">
-        <is>
-          <t>输入</t>
-        </is>
-      </c>
-      <c r="I48" s="21" t="inlineStr">
-        <is>
-          <t>3.3V TTL 230400</t>
-        </is>
-      </c>
-      <c r="J48" s="21" t="inlineStr">
-        <is>
-          <t>需新增引出</t>
-        </is>
-      </c>
-      <c r="K48" s="21" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="L48" s="21" t="inlineStr">
-        <is>
-          <t>★硬件组需新引出。固件已就绪（board.syscfg 提交 ae215b1），引出前实物上VOFA不通</t>
-        </is>
-      </c>
-      <c r="M48" s="25" t="inlineStr">
-        <is>
-          <t>UART_HOST_LINK (=UART5)</t>
-        </is>
-      </c>
-      <c r="N48" s="25" t="inlineStr">
         <is>
           <t>GPIO_UART_HOST_LINK_RX_PIN</t>
         </is>
@@ -4882,7 +4836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4916,66 +4870,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>新增列</t>
+          <t>★编码器迁出晶振脚</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sheet1 M/N 列</t>
+          <t>QEI_LEFT→TIMG9/PB7/PB9；QEI_RIGHT→TIMG8/PB10/PB11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>syscfg 实例名 + 引脚宏</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>固件侧标识，供硬件组与固件对齐命名。全部取自 SysConfig 生成的 Debug/ti_msp_dl_config.h（非人工拼接），以 IOMUX_PINCM 关联引脚，每个宏均已回验在头文件中真实定义。共 41 个引脚有宏。</t>
+          <t>已施工(board.syscfg)，固件构建通过，驱动零改动</t>
+        </is>
+      </c>
+      <c r="D2" s="34" t="inlineStr">
+        <is>
+          <t>根因：原编码器 4 脚里 3 个是核心板晶振/振荡器脚 —— PA3=SYSCTL.LFXIN、PA6=SYSCTL.HFXOUT、PA2=SYSCTL.ROSC。核心板是现成模块，其上实焊晶振与负载电容，固件无法绕过。硬件组旧表「避免核心板晶振功能冲突」备注已指出此事，本次按该约束施工，采纳硬件组的 PB7/PB9/PB10/PB11 方案。
+左右轮与 timer 的绑定随之互换（左轮由 TIMG8 改 TIMG9），但 syscfg 实例名 QEI_LEFT/QEI_RIGHT 继续与物理轮子绑定，固件驱动零改动，不存在左右轮对调风险。
+唯一偏离硬件组方案处：灰度 IN4 取 PB8 而非 PA7（理由见 Sheet1 该行备注）。
+★需硬件组确认：核心板 PA3/PA5/PA6 上是否确有实焊晶振。若无，本次迁移非必需（但无害且释放3脚）。
+★编码器 AB 接线：请按 A相→PB7(左)/PB10(右)、B相→PB9(左)/PB11(右) 接线。固件方向常量按【旧板】极性标定，新板接好后须由用户实测确认（手推左轮前进，速度应为正），必要时固件调整唯一修正点。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>★冲突标注</t>
+          <t>新增列</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sheet1 橙色行（共 11 行）</t>
+          <t>Sheet1 M/N 列</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>表里的功能 ≠ 固件 syscfg 实际归属</t>
+          <t>syscfg 实例名 + 引脚宏</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M/N 两列反映的是【固件当前实际状态】，不是表的诉求。橙色行表示两者不一致，根因是 Q4（编码器⇄灰度引脚对调）尚未施工：固件里 PB7/PB9/PB10/PB11 仍是灰度 IN4/IN5/IN10/IN11，PA7/PA6/PA3/PA2 仍是编码器 QEI_LEFT/QEI_RIGHT，而 PB20/PB14/PB0 尚未配置。待 Q4 获硬件组确认并施工后，这些行会自动一致。此标注不是错误，是进度差异。</t>
+          <t>固件侧标识，供硬件组与固件对齐命名。全部取自 SysConfig 生成的 Debug/ti_msp_dl_config.h（非人工拼接），以 IOMUX_PINCM 关联引脚，每个宏均已回验在头文件中真实定义。共 41 个引脚有宏。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>脚号订正</t>
+          <t>★冲突标注</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>第5行 PA10</t>
+          <t>Sheet1 橙色行（共 11 行）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>58 -&gt; 56</t>
+          <t>表里的功能 ≠ 固件 syscfg 实际归属</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 58 实为其他引脚的脚号</t>
+          <t>M/N 两列反映的是【固件当前实际状态】，不是表的诉求。橙色行表示两者不一致，根因是 Q4（编码器⇄灰度引脚对调）尚未施工：固件里 PB7/PB9/PB10/PB11 仍是灰度 IN4/IN5/IN10/IN11，PA7/PA6/PA3/PA2 仍是编码器 QEI_LEFT/QEI_RIGHT，而 PB20/PB14/PB0 尚未配置。待 Q4 获硬件组确认并施工后，这些行会自动一致。此标注不是错误，是进度差异。</t>
         </is>
       </c>
     </row>
@@ -4987,17 +4945,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>第6行 PA11</t>
+          <t>第5行 PA10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59 -&gt; 57</t>
+          <t>58 -&gt; 56</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 59 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 58 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
@@ -5009,17 +4967,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>第7行 PA8</t>
+          <t>第6行 PA11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>56 -&gt; 54</t>
+          <t>59 -&gt; 57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 56 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 59 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
@@ -5031,17 +4989,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>第8行 PA9</t>
+          <t>第7行 PA8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57 -&gt; 55</t>
+          <t>56 -&gt; 54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 57 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 56 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5011,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>第11行 PA26</t>
+          <t>第8行 PA9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>35 -&gt; 30</t>
+          <t>57 -&gt; 55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 35 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 57 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
@@ -5075,17 +5033,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>第12行 PA25</t>
+          <t>第11行 PA26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>39 -&gt; 26</t>
+          <t>35 -&gt; 30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 39 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 35 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
@@ -5097,246 +5055,288 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>第19行 PB7</t>
+          <t>第12行 PA25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>55 -&gt; 59</t>
+          <t>39 -&gt; 26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TI 器件数据为准；原值 55 实为其他引脚的脚号</t>
+          <t>TI 器件数据为准；原值 39 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>用途变更</t>
+          <t>脚号订正</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>第5/6行 PA10/PA11</t>
+          <t>第19行 PB7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>运行期UART0交陀螺仪 -&gt; 仅BSL烧录</t>
+          <t>55 -&gt; 59</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>用户2026-07-16裁定；固件已配 UART_BSL_ENTRY=UART0/9600/无DMA</t>
+          <t>TI 器件数据为准；原值 55 实为其他引脚的脚号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>裁定确认</t>
+          <t>用途变更</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>第11/12行 陀螺仪</t>
+          <t>第5/6行 PA10/PA11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UART3 PA26/PA25（维持）</t>
+          <t>运行期UART0交陀螺仪 -&gt; 仅BSL烧录</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>用户2026-07-16裁定；board.syscfg 现状即如此，固件零改动</t>
+          <t>用户2026-07-16裁定；固件已配 UART_BSL_ENTRY=UART0/9600/无DMA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>作废</t>
+          <t>裁定确认</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>第41/42行 调试串口</t>
+          <t>第11/12行 陀螺仪</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PA26/PA25 -&gt; 作废</t>
+          <t>UART3 PA26/PA25（维持）</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PA25/PA26 归陀螺仪独占；『与陀螺仪分离』无法在同一对引脚上成立</t>
+          <t>用户2026-07-16裁定；board.syscfg 现状即如此，固件零改动</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>作废</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>第46/47行 VOFA调试串口</t>
+          <t>第41/42行 调试串口</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UART5 PA1(TX,脚34)/PA0(RX,脚33) @230400</t>
+          <t>PA26/PA25 -&gt; 作废</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>★需硬件组新引出；用户2026-07-16裁定</t>
+          <t>PA25/PA26 归陀螺仪独占；『与陀螺仪分离』无法在同一对引脚上成立</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>作废</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sheet2第4行</t>
+          <t>第46/47行 VOFA调试串口</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>陀螺仪迁PA28/PA31 -&gt; 作废</t>
+          <t>UART5 PA1(TX,脚34)/PA0(RX,脚33) @230400</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>用户裁定陀螺仪维持PA25/PA26</t>
+          <t>★需硬件组新引出；用户2026-07-16裁定</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>作废</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sheet2第4行</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>陀螺仪迁PA28/PA31 -&gt; 作废</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>用户裁定陀螺仪维持PA25/PA26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>修正</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Sheet2第5行</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>运行期UART0交陀螺仪 -&gt; 运行期UART0不使用</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>VOFA 迁 UART5</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>【图例】</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>黄=脚号订正</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>绿=新增需求(需硬件组动作)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>橙=表与固件当前不一致(Q4 未施工)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>【仍待硬件组答复】</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>绿=本次已施工(表与固件一致)；黄=需硬件组新引出</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q1 封装</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Sheet2第6行</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>表称统一LQFP-64(PM)；工程board.syscfg配置为LQFP-100(PZ)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>G3519 两种封装都存在，故这是真问题。已核实：两颗芯片LQFP-64下64个脚号对应引脚名完全一致，故Sheet2第6行的兼容性前提成立。但打样实物到底是哪个封装需确认</t>
+          <t>【仍待硬件组答复】</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q4 编码器⇄灰度对调</t>
+          <t>Q1 封装</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sheet1第19-22/32/33/38/39行</t>
+          <t>Sheet2第6行</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>是否按表执行？PA6晶振冲突是否实测确认？</t>
+          <t>表称统一LQFP-64(PM)；工程board.syscfg配置为LQFP-100(PZ)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>★高风险：本次对调同时翻转了timer↔轮归属（现LEFT=TIMG8/RIGHT=TIMG9，表要求左轮=TIMG9/右轮=TIMG8）。若只改引脚不改映射，左右轮数据会静默对调——不报错不崩溃，易误判为PID问题</t>
+          <t>G3519 两种封装都存在，故这是真问题。已核实：两颗芯片LQFP-64下64个脚号对应引脚名完全一致，故Sheet2第6行的兼容性前提成立。但打样实物到底是哪个封装需确认</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Q4 编码器⇄灰度对调</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sheet1第19-22/32/33/38/39行</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>是否按表执行？PA6晶振冲突是否实测确认？</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>★高风险：本次对调同时翻转了timer↔轮归属（现LEFT=TIMG8/RIGHT=TIMG9，表要求左轮=TIMG9/右轮=TIMG8）。若只改引脚不改映射，左右轮数据会静默对调——不报错不崩溃，易误判为PID问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>脚号错误</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Sheet1 共7行</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>PA8/PA9/PA10/PA11 整体偏移+2；PB7 偏差-4；PA26/PA25 填成了PA28/PA31的脚号</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>★请核对PCB实物：若布线是照脚号走的，则无线模块实际接到PB6/PB7而非PA10/PA11。若布线照原理图符号走则仅为文档错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>清理</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>删除 2 行「作废」记录</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>调试串口 PA25/PA26 旧行</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>这些行与陀螺仪行共用 PA25/PA26，状态互相矛盾，硬件组按引脚检索会命中两条打架的记录。调试串口已迁 UART5/PA1/PA0，旧行无保留价值。历史经 git 可追。</t>
         </is>
       </c>
     </row>
